--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/02_WIM2 - Ön Analiz, Kaynak ve Çevreleme/EKG-KLT-FRM-42_garanti_on_analiz_kontrol_listesi_ve_raporu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/02_WIM2 - Ön Analiz, Kaynak ve Çevreleme/EKG-KLT-FRM-42_garanti_on_analiz_kontrol_listesi_ve_raporu.xlsx
@@ -793,7 +793,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-42&amp;C&amp;"Arial,Regular"&amp;11Garanti Ön Analiz Kontrol Listesi ve Raporu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Cam/pencere ön analizine uyarlandı; gözlem, kanıt ve yetkili garanti/ürün kararı ayrıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -941,7 +942,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-42&amp;C&amp;"Arial,Regular"&amp;11Garanti Ön Analiz Kontrol Listesi ve Raporu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Cam/pencere ön analizine uyarlandı; gözlem, kanıt ve yetkili garanti/ürün kararı ayrıldı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>